--- a/jogos_2025-02-10.xlsx
+++ b/jogos_2025-02-10.xlsx
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Lamia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
         <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Z12" t="n">
         <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['9', '45']</t>
+          <t>['4', '16']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45698.54166666666</v>
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lamia</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="M13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
         <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
         <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['4', '16']</t>
+          <t>['9', '45']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45698.54166666666</v>
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['12', '17', '45+2', '62', '86']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '76']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45698.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -2376,25 +2376,25 @@
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC15" t="n">
         <v>1.8</v>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['41', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45698.58333333334</v>
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.21</v>
+        <v>1.74</v>
       </c>
       <c r="M16" t="n">
-        <v>3.41</v>
+        <v>4.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>4.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45698.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['12', '17', '45+2', '62', '86']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45698.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>4</v>
-      </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.9</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.29</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['47', '56']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['59', '78']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['54', '63', '81', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45698.625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AD20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['59', '78']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['54', '63', '81', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['47', '56']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45698.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['13', '18', '76', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45698.66666666666</v>
@@ -3481,81 +3481,81 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="N24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.2</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>1.5</v>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['36', '59']</t>
+          <t>['53', '57', '81']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '60']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45698.66666666666</v>
@@ -3610,81 +3610,81 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>4.33</v>
-      </c>
       <c r="M25" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
         <v>1.5</v>
@@ -3694,25 +3694,25 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['53', '57', '81']</t>
+          <t>['36', '59']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['22', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45698.66666666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '18', '76', '90+4']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45698.66666666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3894,28 +3894,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>3.58</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
         <v>3.5</v>
@@ -3924,53 +3924,53 @@
         <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X27" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45698.6875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4023,28 +4023,28 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.28</v>
+        <v>1.63</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.21</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
         <v>3.5</v>
@@ -4053,31 +4053,31 @@
         <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="X28" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB28" t="n">
         <v>1.18</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4086,20 +4086,20 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45698.6875</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['29', '31', '71']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH29" t="n">
         <v>2.11</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI29" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45698.6875</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>3.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.4</v>
+        <v>2.21</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
         <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="X30" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['29', '31', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.63</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.11</v>
+        <v>1.24</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45698.6875</v>
